--- a/Result/DailyRunRealTimeStock/2026-02-04.xlsx
+++ b/Result/DailyRunRealTimeStock/2026-02-04.xlsx
@@ -465,18 +465,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>60.1</v>
+        <v>25.8</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -486,18 +486,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.8</v>
+        <v>60.1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
